--- a/reports/Debug-purgatory-20260104/For The Week Ending (Actual)_Budget_week_to_date.xlsx
+++ b/reports/Debug-purgatory-20260104/For The Week Ending (Actual)_Budget_week_to_date.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="99">
   <si>
     <t>Department</t>
   </si>
@@ -22,6 +22,36 @@
     <t>D6780</t>
   </si>
   <si>
+    <t>D1000</t>
+  </si>
+  <si>
+    <t>D4054</t>
+  </si>
+  <si>
+    <t>D5206</t>
+  </si>
+  <si>
+    <t>D6700</t>
+  </si>
+  <si>
+    <t>D6720</t>
+  </si>
+  <si>
+    <t>D6730</t>
+  </si>
+  <si>
+    <t>D6790</t>
+  </si>
+  <si>
+    <t>D6800</t>
+  </si>
+  <si>
+    <t>99200</t>
+  </si>
+  <si>
+    <t>D8050</t>
+  </si>
+  <si>
     <t>D1020</t>
   </si>
   <si>
@@ -37,6 +67,39 @@
     <t>D6215</t>
   </si>
   <si>
+    <t>D1030</t>
+  </si>
+  <si>
+    <t>D4056</t>
+  </si>
+  <si>
+    <t>D5208</t>
+  </si>
+  <si>
+    <t>D5810</t>
+  </si>
+  <si>
+    <t>99150</t>
+  </si>
+  <si>
+    <t>D1100</t>
+  </si>
+  <si>
+    <t>D5000</t>
+  </si>
+  <si>
+    <t>D5201</t>
+  </si>
+  <si>
+    <t>D8010</t>
+  </si>
+  <si>
+    <t>D8030</t>
+  </si>
+  <si>
+    <t>D8040</t>
+  </si>
+  <si>
     <t>99100</t>
   </si>
   <si>
@@ -94,66 +157,6 @@
     <t>D8060</t>
   </si>
   <si>
-    <t>99200</t>
-  </si>
-  <si>
-    <t>D8050</t>
-  </si>
-  <si>
-    <t>99150</t>
-  </si>
-  <si>
-    <t>D1100</t>
-  </si>
-  <si>
-    <t>D5000</t>
-  </si>
-  <si>
-    <t>D5201</t>
-  </si>
-  <si>
-    <t>D8030</t>
-  </si>
-  <si>
-    <t>D8040</t>
-  </si>
-  <si>
-    <t>D1030</t>
-  </si>
-  <si>
-    <t>D4056</t>
-  </si>
-  <si>
-    <t>D5208</t>
-  </si>
-  <si>
-    <t>D5810</t>
-  </si>
-  <si>
-    <t>D1000</t>
-  </si>
-  <si>
-    <t>D4054</t>
-  </si>
-  <si>
-    <t>D5206</t>
-  </si>
-  <si>
-    <t>D6700</t>
-  </si>
-  <si>
-    <t>D6720</t>
-  </si>
-  <si>
-    <t>D6730</t>
-  </si>
-  <si>
-    <t>D6790</t>
-  </si>
-  <si>
-    <t>D6800</t>
-  </si>
-  <si>
     <t>Type</t>
   </si>
   <si>
@@ -175,6 +178,36 @@
     <t>Grounds Maintenance</t>
   </si>
   <si>
+    <t>Mountain G&amp;A</t>
+  </si>
+  <si>
+    <t>Purg Sports Resort</t>
+  </si>
+  <si>
+    <t>Hoody's</t>
+  </si>
+  <si>
+    <t>Resort Services G&amp;A</t>
+  </si>
+  <si>
+    <t>Guest Services</t>
+  </si>
+  <si>
+    <t>Security</t>
+  </si>
+  <si>
+    <t>Transportation</t>
+  </si>
+  <si>
+    <t>Commercial Tenants</t>
+  </si>
+  <si>
+    <t>Winter Season Pass Visits  - Home Resort</t>
+  </si>
+  <si>
+    <t>Risk Management</t>
+  </si>
+  <si>
     <t>Lift Maintenance</t>
   </si>
   <si>
@@ -190,6 +223,39 @@
     <t>Housekeeping</t>
   </si>
   <si>
+    <t>Snowmaking</t>
+  </si>
+  <si>
+    <t>Branded</t>
+  </si>
+  <si>
+    <t>Purgy's</t>
+  </si>
+  <si>
+    <t>Events</t>
+  </si>
+  <si>
+    <t>Comp Tickets</t>
+  </si>
+  <si>
+    <t>Vehicle Maintenance</t>
+  </si>
+  <si>
+    <t>F&amp;B Admin</t>
+  </si>
+  <si>
+    <t>Powderhouse</t>
+  </si>
+  <si>
+    <t>General Administration</t>
+  </si>
+  <si>
+    <t>Executive</t>
+  </si>
+  <si>
+    <t>HR</t>
+  </si>
+  <si>
     <t>Daily Winter Ticketed</t>
   </si>
   <si>
@@ -245,66 +311,6 @@
   </si>
   <si>
     <t>IT Services</t>
-  </si>
-  <si>
-    <t>Winter Season Pass Visits  - Home Resort</t>
-  </si>
-  <si>
-    <t>Risk Management</t>
-  </si>
-  <si>
-    <t>Comp Tickets</t>
-  </si>
-  <si>
-    <t>Vehicle Maintenance</t>
-  </si>
-  <si>
-    <t>F&amp;B Admin</t>
-  </si>
-  <si>
-    <t>Powderhouse</t>
-  </si>
-  <si>
-    <t>Executive</t>
-  </si>
-  <si>
-    <t>HR</t>
-  </si>
-  <si>
-    <t>Snowmaking</t>
-  </si>
-  <si>
-    <t>Branded</t>
-  </si>
-  <si>
-    <t>Purgy's</t>
-  </si>
-  <si>
-    <t>Events</t>
-  </si>
-  <si>
-    <t>Mountain G&amp;A</t>
-  </si>
-  <si>
-    <t>Purg Sports Resort</t>
-  </si>
-  <si>
-    <t>Hoody's</t>
-  </si>
-  <si>
-    <t>Resort Services G&amp;A</t>
-  </si>
-  <si>
-    <t>Guest Services</t>
-  </si>
-  <si>
-    <t>Security</t>
-  </si>
-  <si>
-    <t>Transportation</t>
-  </si>
-  <si>
-    <t>Commercial Tenants</t>
   </si>
 </sst>
 </file>
@@ -667,7 +673,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D69"/>
+  <dimension ref="A1:D72"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -681,13 +687,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -695,13 +701,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C2" s="2">
         <v>16516.97</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -709,13 +715,13 @@
         <v>1</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C3" s="2">
         <v>20139.70</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -723,13 +729,13 @@
         <v>2</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C4" s="2">
-        <v>14457.75</v>
+        <v>2485.93</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -737,24 +743,24 @@
         <v>3</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C5" s="2">
-        <v>16444.30</v>
+        <v>4947.30</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>48</v>
       </c>
       <c r="C6" s="2">
-        <v>4160.59</v>
+        <v>175543.61</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>55</v>
@@ -762,13 +768,13 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C7" s="2">
-        <v>727244.71</v>
+        <v>3781.30</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>56</v>
@@ -776,13 +782,13 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>48</v>
       </c>
       <c r="C8" s="2">
-        <v>12138.26</v>
+        <v>18891.39</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>56</v>
@@ -790,13 +796,13 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C9" s="2">
-        <v>4008.69</v>
+        <v>3103.91</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>57</v>
@@ -804,13 +810,13 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C10" s="2">
-        <v>12500.00</v>
+        <v>5040.84</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>57</v>
@@ -818,13 +824,13 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>49</v>
       </c>
       <c r="C11" s="2">
-        <v>15820.00</v>
+        <v>2739.59</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>58</v>
@@ -832,27 +838,27 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>48</v>
       </c>
       <c r="C12" s="2">
-        <v>80943.43</v>
+        <v>16439.00</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C13" s="2">
-        <v>427140.00</v>
+        <v>1322.80</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>59</v>
@@ -860,69 +866,69 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>48</v>
       </c>
       <c r="C14" s="2">
-        <v>3590.04</v>
+        <v>1548.75</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C15" s="2">
-        <v>16913.80</v>
+        <v>12201.25</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C16" s="2">
-        <v>402619.00</v>
+        <v>5892.96</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C17" s="2">
-        <v>101396.48</v>
+        <v>7000.00</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C18" s="2">
-        <v>17618.93</v>
+        <v>14529.00</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>62</v>
@@ -930,13 +936,13 @@
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C19" s="2">
-        <v>33077.08</v>
+        <v>1590.47</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>63</v>
@@ -947,13 +953,13 @@
         <v>12</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C20" s="2">
-        <v>2883.65</v>
+        <v>14457.75</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -961,13 +967,13 @@
         <v>13</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C21" s="2">
-        <v>5114.06</v>
+        <v>16444.30</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -975,13 +981,13 @@
         <v>14</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C22" s="2">
-        <v>5147.08</v>
+        <v>4160.59</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -992,21 +998,21 @@
         <v>48</v>
       </c>
       <c r="C23" s="2">
-        <v>43560.69</v>
+        <v>1151970.37</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C24" s="2">
-        <v>5690.30</v>
+        <v>12138.26</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>67</v>
@@ -1014,13 +1020,13 @@
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C25" s="2">
-        <v>35081.41</v>
+        <v>4008.69</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>68</v>
@@ -1028,27 +1034,27 @@
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>48</v>
       </c>
       <c r="C26" s="2">
-        <v>9923.53</v>
+        <v>12500.00</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C27" s="2">
-        <v>2263220.28</v>
+        <v>14406.80</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>69</v>
@@ -1056,13 +1062,13 @@
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>48</v>
       </c>
       <c r="C28" s="2">
-        <v>4565.80</v>
+        <v>63015.55</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>70</v>
@@ -1070,13 +1076,13 @@
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C29" s="2">
-        <v>29907.79</v>
+        <v>1890.00</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>70</v>
@@ -1084,13 +1090,13 @@
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C30" s="2">
-        <v>52411.56</v>
+        <v>26319.70</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>71</v>
@@ -1098,13 +1104,13 @@
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>48</v>
       </c>
       <c r="C31" s="2">
-        <v>6056.80</v>
+        <v>242510.64</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>71</v>
@@ -1112,13 +1118,13 @@
     </row>
     <row r="32" spans="1:4">
       <c r="A32" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C32" s="2">
-        <v>1681.41</v>
+        <v>1408.75</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>72</v>
@@ -1126,13 +1132,13 @@
     </row>
     <row r="33" spans="1:4">
       <c r="A33" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C33" s="2">
-        <v>14894.69</v>
+        <v>0.00</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>72</v>
@@ -1140,13 +1146,13 @@
     </row>
     <row r="34" spans="1:4">
       <c r="A34" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C34" s="2">
-        <v>11077.11</v>
+        <v>4816.00</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>73</v>
@@ -1157,13 +1163,13 @@
         <v>22</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C35" s="2">
-        <v>65025.65</v>
+        <v>9849.69</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -1171,27 +1177,27 @@
         <v>23</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C36" s="2">
-        <v>8334.41</v>
+        <v>7462.77</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C37" s="2">
-        <v>12218.15</v>
+        <v>6900.74</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -1202,80 +1208,80 @@
         <v>48</v>
       </c>
       <c r="C38" s="2">
-        <v>7470.03</v>
+        <v>69725.86</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C39" s="2">
-        <v>9202.76</v>
+        <v>2247.84</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="40" spans="1:4">
       <c r="A40" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C40" s="2">
-        <v>5634.22</v>
+        <v>8662.87</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>49</v>
       </c>
       <c r="C41" s="2">
-        <v>14529.00</v>
+        <v>5645.97</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="42" spans="1:4">
       <c r="A42" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C42" s="2">
-        <v>1590.47</v>
+        <v>15820.00</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="43" spans="1:4">
       <c r="A43" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>49</v>
       </c>
       <c r="C43" s="2">
-        <v>4816.00</v>
+        <v>80943.43</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -1286,10 +1292,10 @@
         <v>48</v>
       </c>
       <c r="C44" s="2">
-        <v>9849.69</v>
+        <v>427140.00</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -1297,24 +1303,24 @@
         <v>30</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C45" s="2">
-        <v>7462.77</v>
+        <v>3590.04</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="46" spans="1:4">
       <c r="A46" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>48</v>
       </c>
       <c r="C46" s="2">
-        <v>6900.74</v>
+        <v>9494.55</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>82</v>
@@ -1325,24 +1331,24 @@
         <v>31</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C47" s="2">
-        <v>69725.86</v>
+        <v>402619.00</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="48" spans="1:4">
       <c r="A48" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C48" s="2">
-        <v>8662.87</v>
+        <v>16913.80</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>83</v>
@@ -1350,13 +1356,13 @@
     </row>
     <row r="49" spans="1:4">
       <c r="A49" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>48</v>
       </c>
       <c r="C49" s="2">
-        <v>5645.97</v>
+        <v>101396.48</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>84</v>
@@ -1364,69 +1370,69 @@
     </row>
     <row r="50" spans="1:4">
       <c r="A50" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C50" s="2">
-        <v>14406.80</v>
+        <v>17618.93</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="51" spans="1:4">
       <c r="A51" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C51" s="2">
-        <v>58514.46</v>
+        <v>33077.08</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="52" spans="1:4">
       <c r="A52" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C52" s="2">
-        <v>1890.00</v>
+        <v>2883.65</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="53" spans="1:4">
       <c r="A53" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C53" s="2">
-        <v>26319.70</v>
+        <v>5114.06</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="54" spans="1:4">
       <c r="A54" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C54" s="2">
-        <v>242510.64</v>
+        <v>5147.08</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>87</v>
@@ -1434,13 +1440,13 @@
     </row>
     <row r="55" spans="1:4">
       <c r="A55" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C55" s="2">
-        <v>1408.75</v>
+        <v>43560.69</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>88</v>
@@ -1451,13 +1457,13 @@
         <v>37</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C56" s="2">
-        <v>0.00</v>
+        <v>5690.30</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -1465,13 +1471,13 @@
         <v>38</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C57" s="2">
-        <v>2485.93</v>
+        <v>35081.41</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -1479,13 +1485,13 @@
         <v>39</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C58" s="2">
-        <v>4947.30</v>
+        <v>9923.53</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -1493,13 +1499,13 @@
         <v>39</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C59" s="2">
-        <v>163728.19</v>
+        <v>2263220.28</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -1507,13 +1513,13 @@
         <v>40</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C60" s="2">
-        <v>3781.30</v>
+        <v>4565.80</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -1521,13 +1527,13 @@
         <v>40</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C61" s="2">
-        <v>18891.39</v>
+        <v>36923.19</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -1538,21 +1544,21 @@
         <v>48</v>
       </c>
       <c r="C62" s="2">
-        <v>3103.91</v>
+        <v>55382.99</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="63" spans="1:4">
       <c r="A63" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C63" s="2">
-        <v>2739.59</v>
+        <v>6056.80</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>93</v>
@@ -1563,24 +1569,24 @@
         <v>42</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C64" s="2">
-        <v>16439.00</v>
+        <v>1681.41</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="65" spans="1:4">
       <c r="A65" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>48</v>
       </c>
       <c r="C65" s="2">
-        <v>1322.80</v>
+        <v>14894.69</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>94</v>
@@ -1591,24 +1597,24 @@
         <v>43</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C66" s="2">
-        <v>1548.75</v>
+        <v>11077.11</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="67" spans="1:4">
       <c r="A67" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>48</v>
       </c>
       <c r="C67" s="2">
-        <v>12201.25</v>
+        <v>65025.65</v>
       </c>
       <c r="D67" s="2" t="s">
         <v>95</v>
@@ -1619,27 +1625,69 @@
         <v>44</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C68" s="2">
-        <v>5892.96</v>
+        <v>8334.41</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="69" spans="1:4">
       <c r="A69" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C69" s="2">
-        <v>7000.00</v>
+        <v>12218.15</v>
       </c>
       <c r="D69" s="2" t="s">
         <v>96</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4">
+      <c r="A70" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C70" s="2">
+        <v>7470.03</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4">
+      <c r="A71" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C71" s="2">
+        <v>11450.53</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4">
+      <c r="A72" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C72" s="2">
+        <v>5634.22</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>98</v>
       </c>
     </row>
   </sheetData>
